--- a/event_planner_forms/027_event_florist_referral_form--event_planner_forms.xlsx
+++ b/event_planner_forms/027_event_florist_referral_form--event_planner_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Event Type</t>
+          <t>Event Type 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Event Date</t>
+          <t>Event Date 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Event Time</t>
+          <t>Event Time 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Event Location</t>
+          <t>Event Location 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Event URL</t>
+          <t>Event Url 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Referral Fee</t>
+          <t>Vendor Referral Fee 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'wedding'}</t>
+          <t>wedding</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Wedding'}</t>
+          <t>Wedding</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'corporate'}</t>
+          <t>corporate</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Corporate'}</t>
+          <t>Corporate</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'wedding'}</t>
+          <t>wedding</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Wedding'}</t>
+          <t>Wedding</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'corporate'}</t>
+          <t>corporate</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Corporate'}</t>
+          <t>Corporate</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
